--- a/ET-release8.1/Unity/Assets/Config/Excel/ActionsConfig.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/ActionsConfig.xlsx
@@ -14,12 +14,20 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="4">
   <si>
     <t>Id</t>
   </si>
   <si>
     <t>int</t>
+  </si>
+  <si>
+    <t>技能行为类型</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Type</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -391,56 +399,70 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="C3:C14"/>
+  <dimension ref="C3:D14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
     <col min="2" max="2" width="12.75" style="2" customWidth="1"/>
-    <col min="3" max="3" width="12.625" style="2" customWidth="1"/>
-    <col min="4" max="16384" width="9" style="2"/>
+    <col min="3" max="4" width="12.625" style="2" customWidth="1"/>
+    <col min="5" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C3" s="3" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="D3" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C4" s="3" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="D4" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C5" s="3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="3:3" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="D5" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="3:4" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C6" s="1">
         <v>7700001</v>
       </c>
     </row>
-    <row r="7" spans="3:3" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="3:4" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C7" s="1">
         <v>7700002</v>
       </c>
     </row>
-    <row r="8" spans="3:3" s="1" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="9" spans="3:3" s="1" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="10" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="3:4" s="1" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="9" spans="3:4" s="1" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="10" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C10" s="1"/>
-    </row>
-    <row r="11" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="D10" s="1"/>
+    </row>
+    <row r="11" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C11" s="1"/>
-    </row>
-    <row r="12" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="D11" s="1"/>
+    </row>
+    <row r="12" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C12" s="1"/>
-    </row>
-    <row r="13" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="D12" s="1"/>
+    </row>
+    <row r="13" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C13" s="1"/>
-    </row>
-    <row r="14" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="D13" s="1"/>
+    </row>
+    <row r="14" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/ET-release8.1/Unity/Assets/Config/Excel/ActionsConfig.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/ActionsConfig.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="7">
   <si>
     <t>Id</t>
   </si>
@@ -27,6 +27,18 @@
   </si>
   <si>
     <t>Type</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>行为参数</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ActionsParam</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>int[]</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -399,70 +411,84 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="C3:D14"/>
+  <dimension ref="C3:E14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
     <col min="2" max="2" width="12.75" style="2" customWidth="1"/>
-    <col min="3" max="4" width="12.625" style="2" customWidth="1"/>
-    <col min="5" max="16384" width="9" style="2"/>
+    <col min="3" max="5" width="12.625" style="2" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="E3" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="E4" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C5" s="3" t="s">
         <v>1</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="3:4" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="E5" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C6" s="1">
         <v>7700001</v>
       </c>
     </row>
-    <row r="7" spans="3:4" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C7" s="1">
         <v>7700002</v>
       </c>
     </row>
-    <row r="8" spans="3:4" s="1" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="9" spans="3:4" s="1" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="10" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="9" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="10" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
-    </row>
-    <row r="11" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="E10" s="1"/>
+    </row>
+    <row r="11" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
-    </row>
-    <row r="12" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="E11" s="1"/>
+    </row>
+    <row r="12" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
-    </row>
-    <row r="13" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="E12" s="1"/>
+    </row>
+    <row r="13" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
-    </row>
-    <row r="14" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="E13" s="1"/>
+    </row>
+    <row r="14" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/ET-release8.1/Unity/Assets/Config/Excel/ActionsConfig.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/ActionsConfig.xlsx
@@ -455,12 +455,18 @@
     </row>
     <row r="6" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C6" s="1">
-        <v>7700001</v>
+        <v>77001</v>
+      </c>
+      <c r="D6" s="1">
+        <v>2</v>
+      </c>
+      <c r="E6" s="1">
+        <v>-10</v>
       </c>
     </row>
     <row r="7" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C7" s="1">
-        <v>7700002</v>
+        <v>77002</v>
       </c>
     </row>
     <row r="8" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.15"/>

--- a/ET-release8.1/Unity/Assets/Config/Excel/ActionsConfig.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/ActionsConfig.xlsx
@@ -461,12 +461,18 @@
         <v>2</v>
       </c>
       <c r="E6" s="1">
-        <v>-10</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="7" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C7" s="1">
         <v>77002</v>
+      </c>
+      <c r="D7" s="1">
+        <v>2</v>
+      </c>
+      <c r="E7" s="1">
+        <v>-50</v>
       </c>
     </row>
     <row r="8" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.15"/>

--- a/ET-release8.1/Unity/Assets/Config/Excel/ActionsConfig.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/ActionsConfig.xlsx
@@ -475,7 +475,17 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="8" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="8" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C8" s="1">
+        <v>77003</v>
+      </c>
+      <c r="D8" s="1">
+        <v>2</v>
+      </c>
+      <c r="E8" s="1">
+        <v>-2</v>
+      </c>
+    </row>
     <row r="9" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.15"/>
     <row r="10" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C10" s="1"/>

--- a/ET-release8.1/Unity/Assets/Config/Excel/ActionsConfig.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/ActionsConfig.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Git\FAE\ETMMO\ET-release8.1\Unity\Assets\Config\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F5105A0-3950-41DA-8EDD-63142F15AC40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28695" windowHeight="13065"/>
+    <workbookView xWindow="345" yWindow="2745" windowWidth="24630" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ActionsProto" sheetId="1" r:id="rId1"/>
@@ -14,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="17">
   <si>
     <t>Id</t>
   </si>
@@ -39,13 +45,48 @@
   </si>
   <si>
     <t>int[]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>描述</t>
+  </si>
+  <si>
+    <t>Desc</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>单体攻击</t>
+  </si>
+  <si>
+    <t>单体攻击</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>假子弹</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>22002,300</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>-5</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>buff持续掉血</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -103,13 +144,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -120,14 +164,17 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -165,7 +212,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -237,7 +284,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -410,17 +457,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="C3:E14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="C2:F14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
     <col min="2" max="2" width="12.75" style="2" customWidth="1"/>
     <col min="3" max="5" width="12.625" style="2" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="2"/>
+    <col min="6" max="6" width="28.75" style="2" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="F2" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C3" s="3" t="s">
         <v>0</v>
       </c>
@@ -430,8 +483,11 @@
       <c r="E3" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="F3" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C4" s="3" t="s">
         <v>0</v>
       </c>
@@ -441,8 +497,11 @@
       <c r="E4" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="F4" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C5" s="3" t="s">
         <v>1</v>
       </c>
@@ -452,8 +511,11 @@
       <c r="E5" s="3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="6" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="F5" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="3:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C6" s="1">
         <v>77001</v>
       </c>
@@ -463,8 +525,11 @@
       <c r="E6" s="1">
         <v>-100</v>
       </c>
-    </row>
-    <row r="7" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="F6" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="3:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C7" s="1">
         <v>77002</v>
       </c>
@@ -474,40 +539,59 @@
       <c r="E7" s="1">
         <v>-50</v>
       </c>
-    </row>
-    <row r="8" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="F7" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="3:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C8" s="1">
         <v>77003</v>
       </c>
       <c r="D8" s="1">
+        <v>4</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="3:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="C9" s="1">
+        <v>77004</v>
+      </c>
+      <c r="D9" s="1">
         <v>2</v>
       </c>
-      <c r="E8" s="1">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="9" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="10" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="E9" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
     </row>
-    <row r="11" spans="3:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
     </row>
-    <row r="12" spans="3:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
     </row>
-    <row r="13" spans="3:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
     </row>
-    <row r="14" spans="3:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>

--- a/ET-release8.1/Unity/Assets/Config/Excel/ActionsConfig.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/ActionsConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Git\FAE\ETMMO\ET-release8.1\Unity\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F5105A0-3950-41DA-8EDD-63142F15AC40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C779AC8-EA46-4F3F-9065-D58B49DB4034}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="345" yWindow="2745" windowWidth="24630" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="3390" windowWidth="24630" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ActionsProto" sheetId="1" r:id="rId1"/>
@@ -75,11 +75,11 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
+    <t>buff持续掉血</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <t>-5</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>buff持续掉血</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -565,10 +565,10 @@
         <v>2</v>
       </c>
       <c r="E9" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="10" spans="3:6" x14ac:dyDescent="0.3">

--- a/ET-release8.1/Unity/Assets/Config/Excel/ActionsConfig.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/ActionsConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Git\FAE\ETMMO\ET-release8.1\Unity\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C779AC8-EA46-4F3F-9065-D58B49DB4034}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{447EECCE-A20E-43AF-AC52-12F1D4030282}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="3390" windowWidth="24630" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="810" yWindow="3285" windowWidth="24630" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ActionsProto" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
   <si>
     <t>Id</t>
   </si>
@@ -79,7 +79,27 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>-5</t>
+    <t>buff减攻击力</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>10201,-5</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>属性|物理还是魔法（0物理，1魔法）|固定值(0正常，1固定)|值</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,0,0,-150</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,0,0,-120</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,0,1,-3</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -458,16 +478,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C2:F14"/>
+  <dimension ref="C1:F14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
     <col min="2" max="2" width="12.75" style="2" customWidth="1"/>
-    <col min="3" max="5" width="12.625" style="2" customWidth="1"/>
+    <col min="3" max="4" width="12.625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="63.875" style="2" customWidth="1"/>
     <col min="6" max="6" width="28.75" style="2" customWidth="1"/>
     <col min="7" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
+    <row r="1" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="E1" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
     <row r="2" spans="3:6" x14ac:dyDescent="0.3">
       <c r="F2" s="2" t="s">
         <v>7</v>
@@ -522,8 +548,8 @@
       <c r="D6" s="1">
         <v>2</v>
       </c>
-      <c r="E6" s="1">
-        <v>-100</v>
+      <c r="E6" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>12</v>
@@ -536,8 +562,8 @@
       <c r="D7" s="1">
         <v>2</v>
       </c>
-      <c r="E7" s="1">
-        <v>-50</v>
+      <c r="E7" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>11</v>
@@ -564,17 +590,26 @@
       <c r="D9" s="1">
         <v>2</v>
       </c>
-      <c r="E9" s="4" t="s">
-        <v>16</v>
+      <c r="E9" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="10" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
+      <c r="C10" s="1">
+        <v>77005</v>
+      </c>
+      <c r="D10" s="1">
+        <v>1</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="11" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C11" s="1"/>
